--- a/chair_classification_results.xlsx
+++ b/chair_classification_results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af69c26be6256a92/work/会社アプリ関連/チェア修理アプリ用/修理アプリファイル/ファイル名変更セット/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af69c26be6256a92/work/会社アプリ関連/チェア修理アプリ用/修理アプリファイル/githubアップロードセット/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="100" documentId="13_ncr:1_{6AE3DB7E-1305-4CAA-81DE-418CEC821CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83E0AF26-D8C0-4AB5-B036-D3B08B5E4428}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="13_ncr:1_{6AE3DB7E-1305-4CAA-81DE-418CEC821CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3CB7533-5A02-43DF-AE41-8B25F4E3B053}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="361">
   <si>
     <t>ファイル名</t>
   </si>
@@ -1145,6 +1145,10 @@
   </si>
   <si>
     <t>No788.jpg</t>
+  </si>
+  <si>
+    <t>MC03.jpg</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -1545,12 +1549,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E353"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E354"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="74.81640625" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="74.77734375" customWidth="1"/>
+    <col min="5" max="5" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -4910,78 +4914,78 @@
       <c r="E222" s="3"/>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A223" s="3" t="s">
+      <c r="A223" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E223" s="3"/>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A224" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B223" s="3" t="s">
+      <c r="B224" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C223" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D223" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E223" s="3">
+      <c r="C224" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E224" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A224" s="2" t="s">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A225" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B224" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C224" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D224" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E224" s="3"/>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A225" s="3" t="s">
+      <c r="B225" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E225" s="3"/>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A226" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B225" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C225" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D225" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E225" s="3">
+      <c r="B226" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E226" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A226" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B226" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C226" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D226" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E226" s="3"/>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A227" s="2" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B227" s="3" t="s">
-        <v>8</v>
+        <v>114</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D227" s="3" t="s">
         <v>7</v>
@@ -4990,10 +4994,10 @@
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A228" s="2" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C228" s="3" t="s">
         <v>5</v>
@@ -5005,25 +5009,25 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A229" s="2" t="s">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C229" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E229" s="3"/>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A230" s="2" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="C230" s="3" t="s">
         <v>5</v>
@@ -5035,37 +5039,37 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A231" s="2" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>8</v>
+        <v>114</v>
       </c>
       <c r="C231" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E231" s="3"/>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A232" s="2" t="s">
-        <v>191</v>
+        <v>87</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C232" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E232" s="3"/>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A233" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>4</v>
@@ -5083,7 +5087,7 @@
         <v>192</v>
       </c>
       <c r="B234" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C234" s="3" t="s">
         <v>5</v>
@@ -5095,10 +5099,10 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A235" s="2" t="s">
-        <v>49</v>
+        <v>192</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C235" s="3" t="s">
         <v>5</v>
@@ -5110,7 +5114,7 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A236" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>4</v>
@@ -5125,7 +5129,7 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A237" s="2" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="B237" s="3" t="s">
         <v>4</v>
@@ -5134,16 +5138,16 @@
         <v>5</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E237" s="3"/>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A238" s="2" t="s">
-        <v>261</v>
+        <v>91</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>116</v>
+        <v>4</v>
       </c>
       <c r="C238" s="3" t="s">
         <v>5</v>
@@ -5155,7 +5159,7 @@
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A239" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>116</v>
@@ -5170,22 +5174,22 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A240" s="2" t="s">
-        <v>99</v>
+        <v>262</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="C240" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E240" s="3"/>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A241" s="2" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>8</v>
@@ -5194,28 +5198,28 @@
         <v>5</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E241" s="3"/>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A242" s="2" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="C242" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E242" s="3"/>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A243" s="2" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="B243" s="3" t="s">
         <v>116</v>
@@ -5224,58 +5228,58 @@
         <v>5</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E243" s="3"/>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A244" s="2" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E244" s="3"/>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A245" s="2" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E245" s="3"/>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A246" s="2" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C246" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E246" s="3"/>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A247" s="2" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="B247" s="3" t="s">
         <v>10</v>
@@ -5284,22 +5288,22 @@
         <v>5</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E247" s="3"/>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A248" s="6" t="s">
-        <v>108</v>
+      <c r="A248" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C248" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E248" s="3"/>
     </row>
@@ -5308,7 +5312,7 @@
         <v>108</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="C249" s="3" t="s">
         <v>5</v>
@@ -5320,16 +5324,16 @@
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A250" s="6" t="s">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="C250" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E250" s="3"/>
     </row>
@@ -5338,34 +5342,34 @@
         <v>34</v>
       </c>
       <c r="B251" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C251" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E251" s="3"/>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A252" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B252" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C251" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D251" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E251" s="3"/>
-    </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A252" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B252" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="C252" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E252" s="3"/>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A253" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B253" s="3" t="s">
         <v>114</v>
@@ -5380,7 +5384,7 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A254" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B254" s="3" t="s">
         <v>114</v>
@@ -5389,66 +5393,66 @@
         <v>9</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E254" s="3"/>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A255" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E255" s="3"/>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A256" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B255" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C255" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D255" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E255" s="3"/>
-    </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A256" s="4" t="s">
+      <c r="B256" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C256" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E256" s="3"/>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A257" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="B256" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C256" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D256" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E256" s="3">
+      <c r="B257" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C257" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E257" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A257" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="B257" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C257" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D257" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E257" s="3"/>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A258" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D258" s="3" t="s">
         <v>6</v>
@@ -5457,13 +5461,13 @@
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A259" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>8</v>
+        <v>114</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D259" s="3" t="s">
         <v>6</v>
@@ -5472,13 +5476,13 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A260" s="2" t="s">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D260" s="3" t="s">
         <v>6</v>
@@ -5487,7 +5491,7 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A261" s="2" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="B261" s="3" t="s">
         <v>4</v>
@@ -5496,28 +5500,28 @@
         <v>5</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E261" s="3"/>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A262" s="2" t="s">
-        <v>201</v>
+        <v>65</v>
       </c>
       <c r="B262" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E262" s="3"/>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A263" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B263" s="3" t="s">
         <v>4</v>
@@ -5526,28 +5530,28 @@
         <v>9</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E263" s="3"/>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A264" s="2" t="s">
-        <v>105</v>
+        <v>202</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E264" s="3"/>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A265" s="2" t="s">
-        <v>203</v>
+        <v>105</v>
       </c>
       <c r="B265" s="3" t="s">
         <v>4</v>
@@ -5556,34 +5560,34 @@
         <v>5</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E265" s="3"/>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A266" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B266" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E266" s="3"/>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A267" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B267" s="3" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D267" s="3" t="s">
         <v>6</v>
@@ -5592,10 +5596,10 @@
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A268" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="C268" s="3" t="s">
         <v>5</v>
@@ -5607,7 +5611,7 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A269" s="2" t="s">
-        <v>80</v>
+        <v>206</v>
       </c>
       <c r="B269" s="3" t="s">
         <v>4</v>
@@ -5622,7 +5626,7 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A270" s="2" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="B270" s="3" t="s">
         <v>4</v>
@@ -5631,13 +5635,13 @@
         <v>5</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E270" s="3"/>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A271" s="2" t="s">
-        <v>253</v>
+        <v>12</v>
       </c>
       <c r="B271" s="3" t="s">
         <v>4</v>
@@ -5646,7 +5650,7 @@
         <v>5</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E271" s="3"/>
     </row>
@@ -5655,7 +5659,7 @@
         <v>253</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C272" s="3" t="s">
         <v>5</v>
@@ -5667,22 +5671,22 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A273" s="2" t="s">
-        <v>207</v>
+        <v>253</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C273" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E273" s="3"/>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A274" s="2" t="s">
-        <v>40</v>
+        <v>207</v>
       </c>
       <c r="B274" s="3" t="s">
         <v>4</v>
@@ -5691,16 +5695,16 @@
         <v>5</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E274" s="3"/>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A275" s="2" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="B275" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C275" s="3" t="s">
         <v>5</v>
@@ -5712,13 +5716,13 @@
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A276" s="2" t="s">
-        <v>208</v>
+        <v>59</v>
       </c>
       <c r="B276" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D276" s="3" t="s">
         <v>6</v>
@@ -5727,7 +5731,7 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A277" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B277" s="3" t="s">
         <v>8</v>
@@ -5736,13 +5740,13 @@
         <v>9</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E277" s="3"/>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A278" s="2" t="s">
-        <v>28</v>
+        <v>209</v>
       </c>
       <c r="B278" s="3" t="s">
         <v>8</v>
@@ -5751,37 +5755,37 @@
         <v>9</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E278" s="3"/>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A279" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B279" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C279" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D279" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E279" s="3"/>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A280" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B279" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C279" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D279" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E279" s="3"/>
-    </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A280" s="6" t="s">
-        <v>71</v>
-      </c>
       <c r="B280" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C280" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E280" s="3"/>
     </row>
@@ -5790,7 +5794,7 @@
         <v>71</v>
       </c>
       <c r="B281" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C281" s="3" t="s">
         <v>9</v>
@@ -5802,10 +5806,10 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A282" s="6" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C282" s="3" t="s">
         <v>9</v>
@@ -5820,7 +5824,7 @@
         <v>51</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C283" s="3" t="s">
         <v>9</v>
@@ -5831,40 +5835,40 @@
       <c r="E283" s="3"/>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A284" s="4" t="s">
+      <c r="A284" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B284" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C284" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D284" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E284" s="3"/>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A285" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B284" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C284" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D284" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E284" s="3">
+      <c r="B285" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C285" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D285" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E285" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A285" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B285" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C285" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D285" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E285" s="3"/>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A286" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B286" s="3" t="s">
         <v>116</v>
@@ -5873,34 +5877,34 @@
         <v>5</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E286" s="3"/>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A287" s="2" t="s">
-        <v>210</v>
+        <v>104</v>
       </c>
       <c r="B287" s="3" t="s">
-        <v>4</v>
+        <v>116</v>
       </c>
       <c r="C287" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E287" s="3"/>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A288" s="2" t="s">
-        <v>57</v>
+        <v>210</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>116</v>
+        <v>4</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D288" s="3" t="s">
         <v>6</v>
@@ -5909,7 +5913,7 @@
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A289" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B289" s="3" t="s">
         <v>116</v>
@@ -5918,34 +5922,34 @@
         <v>5</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E289" s="3"/>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A290" s="2" t="s">
-        <v>211</v>
+        <v>58</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>4</v>
+        <v>116</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E290" s="3"/>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A291" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>116</v>
+        <v>4</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D291" s="3" t="s">
         <v>6</v>
@@ -5954,7 +5958,7 @@
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A292" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B292" s="3" t="s">
         <v>116</v>
@@ -5963,58 +5967,58 @@
         <v>5</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E292" s="3"/>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A293" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B293" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C293" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E293" s="3"/>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A294" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B294" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C294" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D294" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E294" s="3"/>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A295" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B294" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C294" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D294" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E294" s="3"/>
-    </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A295" s="5" t="s">
-        <v>216</v>
-      </c>
       <c r="B295" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C295" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E295" s="3"/>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A296" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>116</v>
@@ -6023,24 +6027,22 @@
         <v>5</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E296" s="3">
-        <v>1</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="E296" s="3"/>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A297" s="2" t="s">
-        <v>218</v>
+      <c r="A297" s="5" t="s">
+        <v>217</v>
       </c>
       <c r="B297" s="3" t="s">
-        <v>4</v>
+        <v>116</v>
       </c>
       <c r="C297" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E297" s="3">
         <v>1</v>
@@ -6048,7 +6050,7 @@
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A298" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B298" s="3" t="s">
         <v>4</v>
@@ -6057,28 +6059,30 @@
         <v>5</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E298" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="E298" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A299" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B299" s="3" t="s">
-        <v>116</v>
+        <v>4</v>
       </c>
       <c r="C299" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E299" s="3"/>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A300" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>116</v>
@@ -6087,34 +6091,34 @@
         <v>5</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E300" s="3"/>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A301" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B301" s="3" t="s">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E301" s="3"/>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A302" s="2" t="s">
-        <v>38</v>
+        <v>222</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D302" s="3" t="s">
         <v>6</v>
@@ -6123,7 +6127,7 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A303" s="2" t="s">
-        <v>252</v>
+        <v>38</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>4</v>
@@ -6138,7 +6142,7 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A304" s="2" t="s">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>4</v>
@@ -6153,10 +6157,10 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A305" s="2" t="s">
-        <v>46</v>
+        <v>223</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C305" s="3" t="s">
         <v>5</v>
@@ -6168,7 +6172,7 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A306" s="2" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B306" s="3" t="s">
         <v>8</v>
@@ -6177,78 +6181,78 @@
         <v>5</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E306" s="3"/>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A307" s="2" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="B307" s="3" t="s">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="C307" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E307" s="3"/>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A308" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B308" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C308" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D308" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E308" s="3"/>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A309" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B308" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C308" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D308" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E308" s="3"/>
-    </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A309" s="4" t="s">
+      <c r="B309" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C309" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D309" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E309" s="3"/>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A310" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B309" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C309" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D309" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E309" s="3">
+      <c r="B310" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C310" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D310" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E310" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A310" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="B310" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C310" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D310" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E310" s="3"/>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A311" s="6" t="s">
         <v>225</v>
       </c>
       <c r="B311" s="3" t="s">
-        <v>4</v>
+        <v>116</v>
       </c>
       <c r="C311" s="3" t="s">
         <v>5</v>
@@ -6259,11 +6263,11 @@
       <c r="E311" s="3"/>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A312" s="2" t="s">
-        <v>226</v>
+      <c r="A312" s="6" t="s">
+        <v>225</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>116</v>
+        <v>4</v>
       </c>
       <c r="C312" s="3" t="s">
         <v>5</v>
@@ -6275,58 +6279,58 @@
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A313" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="C313" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E313" s="3"/>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A314" s="2" t="s">
-        <v>88</v>
+        <v>227</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="C314" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E314" s="3"/>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A315" s="2" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C315" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E315" s="3"/>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A316" s="2" t="s">
-        <v>228</v>
+        <v>39</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>8</v>
+        <v>114</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D316" s="3" t="s">
         <v>6</v>
@@ -6335,22 +6339,22 @@
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A317" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="C317" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E317" s="3"/>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A318" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>114</v>
@@ -6359,19 +6363,19 @@
         <v>9</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E318" s="3"/>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A319" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>114</v>
       </c>
       <c r="C319" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D319" s="3" t="s">
         <v>6</v>
@@ -6380,10 +6384,10 @@
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A320" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B320" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C320" s="3" t="s">
         <v>5</v>
@@ -6395,7 +6399,7 @@
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A321" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B321" s="3" t="s">
         <v>116</v>
@@ -6404,13 +6408,13 @@
         <v>5</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E321" s="3"/>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A322" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>116</v>
@@ -6419,13 +6423,13 @@
         <v>5</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E322" s="3"/>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A323" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B323" s="3" t="s">
         <v>116</v>
@@ -6434,31 +6438,31 @@
         <v>5</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E323" s="3"/>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A324" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B324" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C324" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D324" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E324" s="3"/>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A325" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B324" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C324" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D324" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E324" s="3"/>
-    </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A325" s="4" t="s">
-        <v>237</v>
-      </c>
       <c r="B325" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C325" s="3" t="s">
         <v>5</v>
@@ -6466,51 +6470,51 @@
       <c r="D325" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E325" s="3">
-        <v>1</v>
-      </c>
+      <c r="E325" s="3"/>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A326" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>4</v>
+        <v>117</v>
       </c>
       <c r="C326" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E326" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A327" s="2" t="s">
-        <v>239</v>
+      <c r="A327" s="4" t="s">
+        <v>238</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>118</v>
+        <v>4</v>
       </c>
       <c r="C327" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E327" s="3"/>
+        <v>7</v>
+      </c>
+      <c r="E327" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A328" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D328" s="3" t="s">
         <v>6</v>
@@ -6519,13 +6523,13 @@
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A329" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D329" s="3" t="s">
         <v>6</v>
@@ -6534,22 +6538,22 @@
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A330" s="2" t="s">
-        <v>43</v>
+        <v>241</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E330" s="3"/>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A331" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>8</v>
@@ -6564,7 +6568,7 @@
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A332" s="2" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>8</v>
@@ -6573,28 +6577,28 @@
         <v>9</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E332" s="3"/>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A333" s="2" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E333" s="3"/>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A334" s="2" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="B334" s="3" t="s">
         <v>114</v>
@@ -6603,16 +6607,16 @@
         <v>5</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E334" s="3"/>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A335" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="C335" s="3" t="s">
         <v>5</v>
@@ -6624,10 +6628,10 @@
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A336" s="2" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="C336" s="3" t="s">
         <v>5</v>
@@ -6639,37 +6643,37 @@
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A337" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C337" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E337" s="3"/>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A338" s="2" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>10</v>
+        <v>115</v>
       </c>
       <c r="C338" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E338" s="3"/>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A339" s="2" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="B339" s="3" t="s">
         <v>10</v>
@@ -6678,13 +6682,13 @@
         <v>5</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E339" s="3"/>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A340" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B340" s="3" t="s">
         <v>10</v>
@@ -6693,13 +6697,13 @@
         <v>5</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E340" s="3"/>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A341" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>10</v>
@@ -6714,7 +6718,7 @@
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A342" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>10</v>
@@ -6723,19 +6727,19 @@
         <v>5</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E342" s="3"/>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A343" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B343" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C343" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D343" s="3" t="s">
         <v>7</v>
@@ -6744,28 +6748,28 @@
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A344" s="2" t="s">
-        <v>242</v>
+        <v>70</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C344" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E344" s="3"/>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A345" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="C345" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D345" s="3" t="s">
         <v>6</v>
@@ -6774,7 +6778,7 @@
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A346" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B346" s="3" t="s">
         <v>114</v>
@@ -6783,13 +6787,13 @@
         <v>5</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E346" s="3"/>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A347" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B347" s="3" t="s">
         <v>114</v>
@@ -6798,13 +6802,13 @@
         <v>5</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E347" s="3"/>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A348" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>114</v>
@@ -6819,7 +6823,7 @@
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A349" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B349" s="3" t="s">
         <v>114</v>
@@ -6828,13 +6832,13 @@
         <v>5</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E349" s="3"/>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A350" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B350" s="3" t="s">
         <v>114</v>
@@ -6843,13 +6847,13 @@
         <v>5</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E350" s="3"/>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A351" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B351" s="3" t="s">
         <v>114</v>
@@ -6858,43 +6862,58 @@
         <v>5</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E351" s="3"/>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A352" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="C352" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E352" s="3"/>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A353" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B353" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C353" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D353" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E353" s="3"/>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A354" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B353" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C353" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D353" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E353" s="3"/>
+      <c r="B354" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C354" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D354" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E354" s="3"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D353">
-    <sortCondition ref="A2:A353"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D354">
+    <sortCondition ref="A2:A354"/>
   </sortState>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/chair_classification_results.xlsx
+++ b/chair_classification_results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af69c26be6256a92/work/会社アプリ関連/チェア修理アプリ用/修理アプリファイル/githubアップロードセット/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="104" documentId="13_ncr:1_{6AE3DB7E-1305-4CAA-81DE-418CEC821CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A3CB7533-5A02-43DF-AE41-8B25F4E3B053}"/>
+  <xr:revisionPtr revIDLastSave="108" documentId="13_ncr:1_{6AE3DB7E-1305-4CAA-81DE-418CEC821CA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2740DDF1-C247-4351-A21B-F71DBCB39B14}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1421" uniqueCount="362">
   <si>
     <t>ファイル名</t>
   </si>
@@ -1148,6 +1148,10 @@
   </si>
   <si>
     <t>MC03.jpg</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>MC10.jpg</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1262,6 +1266,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1549,7 +1557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E354"/>
+  <dimension ref="A1:E355"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.6640625" bestFit="1" customWidth="1"/>
@@ -4929,78 +4937,78 @@
       <c r="E223" s="3"/>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A224" s="3" t="s">
+      <c r="A224" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E224" s="3"/>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A225" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B224" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C224" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D224" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E224" s="3">
+      <c r="B225" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E225" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A225" s="2" t="s">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A226" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B225" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C225" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D225" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E225" s="3"/>
-    </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A226" s="3" t="s">
+      <c r="B226" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E226" s="3"/>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A227" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B226" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C226" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D226" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E226" s="3">
+      <c r="B227" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C227" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E227" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A227" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B227" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C227" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D227" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E227" s="3"/>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A228" s="2" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B228" s="3" t="s">
-        <v>8</v>
+        <v>114</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D228" s="3" t="s">
         <v>7</v>
@@ -5009,10 +5017,10 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A229" s="2" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C229" s="3" t="s">
         <v>5</v>
@@ -5024,25 +5032,25 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A230" s="2" t="s">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C230" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E230" s="3"/>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A231" s="2" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="C231" s="3" t="s">
         <v>5</v>
@@ -5054,37 +5062,37 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A232" s="2" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>8</v>
+        <v>114</v>
       </c>
       <c r="C232" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E232" s="3"/>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A233" s="2" t="s">
-        <v>191</v>
+        <v>87</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C233" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E233" s="3"/>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A234" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>4</v>
@@ -5102,7 +5110,7 @@
         <v>192</v>
       </c>
       <c r="B235" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C235" s="3" t="s">
         <v>5</v>
@@ -5114,10 +5122,10 @@
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A236" s="2" t="s">
-        <v>49</v>
+        <v>192</v>
       </c>
       <c r="B236" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C236" s="3" t="s">
         <v>5</v>
@@ -5129,7 +5137,7 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A237" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B237" s="3" t="s">
         <v>4</v>
@@ -5144,7 +5152,7 @@
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A238" s="2" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="B238" s="3" t="s">
         <v>4</v>
@@ -5153,16 +5161,16 @@
         <v>5</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E238" s="3"/>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A239" s="2" t="s">
-        <v>261</v>
+        <v>91</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>116</v>
+        <v>4</v>
       </c>
       <c r="C239" s="3" t="s">
         <v>5</v>
@@ -5174,7 +5182,7 @@
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A240" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>116</v>
@@ -5189,22 +5197,22 @@
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A241" s="2" t="s">
-        <v>99</v>
+        <v>262</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="C241" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E241" s="3"/>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A242" s="2" t="s">
-        <v>21</v>
+        <v>99</v>
       </c>
       <c r="B242" s="3" t="s">
         <v>8</v>
@@ -5213,28 +5221,28 @@
         <v>5</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E242" s="3"/>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A243" s="2" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="B243" s="3" t="s">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="C243" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E243" s="3"/>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A244" s="2" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="B244" s="3" t="s">
         <v>116</v>
@@ -5243,58 +5251,58 @@
         <v>5</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E244" s="3"/>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A245" s="2" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E245" s="3"/>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A246" s="2" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E246" s="3"/>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A247" s="2" t="s">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C247" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E247" s="3"/>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A248" s="2" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>10</v>
@@ -5303,22 +5311,22 @@
         <v>5</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E248" s="3"/>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A249" s="6" t="s">
-        <v>108</v>
+      <c r="A249" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C249" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E249" s="3"/>
     </row>
@@ -5327,7 +5335,7 @@
         <v>108</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="C250" s="3" t="s">
         <v>5</v>
@@ -5339,16 +5347,16 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A251" s="6" t="s">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="C251" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E251" s="3"/>
     </row>
@@ -5357,7 +5365,7 @@
         <v>34</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="C252" s="3" t="s">
         <v>5</v>
@@ -5368,23 +5376,23 @@
       <c r="E252" s="3"/>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A253" s="2" t="s">
-        <v>193</v>
+      <c r="A253" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="B253" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E253" s="3"/>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A254" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B254" s="3" t="s">
         <v>114</v>
@@ -5399,7 +5407,7 @@
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A255" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B255" s="3" t="s">
         <v>114</v>
@@ -5408,66 +5416,66 @@
         <v>9</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E255" s="3"/>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A256" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C256" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E256" s="3"/>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A257" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B256" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C256" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D256" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E256" s="3"/>
-    </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A257" s="4" t="s">
+      <c r="B257" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C257" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E257" s="3"/>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A258" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="B257" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C257" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D257" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E257" s="3">
+      <c r="B258" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C258" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E258" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A258" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="B258" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C258" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D258" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E258" s="3"/>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A259" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B259" s="3" t="s">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D259" s="3" t="s">
         <v>6</v>
@@ -5476,13 +5484,13 @@
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A260" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>8</v>
+        <v>114</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D260" s="3" t="s">
         <v>6</v>
@@ -5491,13 +5499,13 @@
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A261" s="2" t="s">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="B261" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D261" s="3" t="s">
         <v>6</v>
@@ -5506,7 +5514,7 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A262" s="2" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="B262" s="3" t="s">
         <v>4</v>
@@ -5515,28 +5523,28 @@
         <v>5</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E262" s="3"/>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A263" s="2" t="s">
-        <v>201</v>
+        <v>65</v>
       </c>
       <c r="B263" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E263" s="3"/>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A264" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>4</v>
@@ -5545,28 +5553,28 @@
         <v>9</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E264" s="3"/>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A265" s="2" t="s">
-        <v>105</v>
+        <v>202</v>
       </c>
       <c r="B265" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E265" s="3"/>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A266" s="2" t="s">
-        <v>203</v>
+        <v>105</v>
       </c>
       <c r="B266" s="3" t="s">
         <v>4</v>
@@ -5575,34 +5583,34 @@
         <v>5</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E266" s="3"/>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A267" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B267" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E267" s="3"/>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A268" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D268" s="3" t="s">
         <v>6</v>
@@ -5611,10 +5619,10 @@
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A269" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="C269" s="3" t="s">
         <v>5</v>
@@ -5626,7 +5634,7 @@
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A270" s="2" t="s">
-        <v>80</v>
+        <v>206</v>
       </c>
       <c r="B270" s="3" t="s">
         <v>4</v>
@@ -5641,7 +5649,7 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A271" s="2" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="B271" s="3" t="s">
         <v>4</v>
@@ -5650,13 +5658,13 @@
         <v>5</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E271" s="3"/>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A272" s="2" t="s">
-        <v>253</v>
+        <v>12</v>
       </c>
       <c r="B272" s="3" t="s">
         <v>4</v>
@@ -5665,7 +5673,7 @@
         <v>5</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E272" s="3"/>
     </row>
@@ -5674,7 +5682,7 @@
         <v>253</v>
       </c>
       <c r="B273" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C273" s="3" t="s">
         <v>5</v>
@@ -5686,22 +5694,22 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A274" s="2" t="s">
-        <v>207</v>
+        <v>253</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C274" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E274" s="3"/>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A275" s="2" t="s">
-        <v>40</v>
+        <v>207</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>4</v>
@@ -5710,16 +5718,16 @@
         <v>5</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E275" s="3"/>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A276" s="2" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C276" s="3" t="s">
         <v>5</v>
@@ -5731,13 +5739,13 @@
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A277" s="2" t="s">
-        <v>208</v>
+        <v>59</v>
       </c>
       <c r="B277" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D277" s="3" t="s">
         <v>6</v>
@@ -5746,7 +5754,7 @@
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A278" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B278" s="3" t="s">
         <v>8</v>
@@ -5755,13 +5763,13 @@
         <v>9</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E278" s="3"/>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A279" s="2" t="s">
-        <v>28</v>
+        <v>209</v>
       </c>
       <c r="B279" s="3" t="s">
         <v>8</v>
@@ -5770,37 +5778,37 @@
         <v>9</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E279" s="3"/>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A280" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B280" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C280" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D280" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E280" s="3"/>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A281" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B280" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C280" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D280" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E280" s="3"/>
-    </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A281" s="6" t="s">
-        <v>71</v>
-      </c>
       <c r="B281" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C281" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E281" s="3"/>
     </row>
@@ -5809,7 +5817,7 @@
         <v>71</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C282" s="3" t="s">
         <v>9</v>
@@ -5821,10 +5829,10 @@
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A283" s="6" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="B283" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C283" s="3" t="s">
         <v>9</v>
@@ -5839,7 +5847,7 @@
         <v>51</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C284" s="3" t="s">
         <v>9</v>
@@ -5850,40 +5858,40 @@
       <c r="E284" s="3"/>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A285" s="4" t="s">
+      <c r="A285" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B285" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C285" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D285" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E285" s="3"/>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A286" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B285" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C285" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D285" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E285" s="3">
+      <c r="B286" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C286" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D286" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E286" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A286" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B286" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C286" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D286" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E286" s="3"/>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A287" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B287" s="3" t="s">
         <v>116</v>
@@ -5892,34 +5900,34 @@
         <v>5</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E287" s="3"/>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A288" s="2" t="s">
-        <v>210</v>
+        <v>104</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>4</v>
+        <v>116</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E288" s="3"/>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A289" s="2" t="s">
-        <v>57</v>
+        <v>210</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>116</v>
+        <v>4</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D289" s="3" t="s">
         <v>6</v>
@@ -5928,7 +5936,7 @@
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A290" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B290" s="3" t="s">
         <v>116</v>
@@ -5937,34 +5945,34 @@
         <v>5</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E290" s="3"/>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A291" s="2" t="s">
-        <v>211</v>
+        <v>58</v>
       </c>
       <c r="B291" s="3" t="s">
-        <v>4</v>
+        <v>116</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E291" s="3"/>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A292" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>116</v>
+        <v>4</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D292" s="3" t="s">
         <v>6</v>
@@ -5973,7 +5981,7 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A293" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B293" s="3" t="s">
         <v>116</v>
@@ -5982,84 +5990,82 @@
         <v>5</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E293" s="3"/>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A294" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C294" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E294" s="3"/>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A295" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B295" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C295" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D295" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E295" s="3"/>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A296" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B295" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C295" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D295" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E295" s="3"/>
-    </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A296" s="5" t="s">
-        <v>216</v>
-      </c>
       <c r="B296" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C296" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E296" s="3"/>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A297" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B297" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C297" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D297" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E297" s="3"/>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A298" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B297" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C297" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D297" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E297" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A298" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="B298" s="3" t="s">
-        <v>4</v>
+        <v>116</v>
       </c>
       <c r="C298" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E298" s="3">
         <v>1</v>
@@ -6067,7 +6073,7 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A299" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>4</v>
@@ -6076,28 +6082,30 @@
         <v>5</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E299" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="E299" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A300" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B300" s="3" t="s">
-        <v>116</v>
+        <v>4</v>
       </c>
       <c r="C300" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E300" s="3"/>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A301" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>116</v>
@@ -6106,34 +6114,34 @@
         <v>5</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E301" s="3"/>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A302" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E302" s="3"/>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A303" s="2" t="s">
-        <v>38</v>
+        <v>222</v>
       </c>
       <c r="B303" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D303" s="3" t="s">
         <v>6</v>
@@ -6142,7 +6150,7 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A304" s="2" t="s">
-        <v>252</v>
+        <v>38</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>4</v>
@@ -6157,7 +6165,7 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A305" s="2" t="s">
-        <v>223</v>
+        <v>252</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>4</v>
@@ -6172,10 +6180,10 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A306" s="2" t="s">
-        <v>46</v>
+        <v>223</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C306" s="3" t="s">
         <v>5</v>
@@ -6187,7 +6195,7 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A307" s="2" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B307" s="3" t="s">
         <v>8</v>
@@ -6196,78 +6204,78 @@
         <v>5</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E307" s="3"/>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A308" s="2" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="C308" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E308" s="3"/>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A309" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B309" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C309" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D309" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E309" s="3"/>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A310" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B309" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C309" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D309" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E309" s="3"/>
-    </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A310" s="4" t="s">
+      <c r="B310" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C310" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D310" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E310" s="3"/>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A311" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B310" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C310" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D310" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E310" s="3">
+      <c r="B311" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C311" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D311" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E311" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A311" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="B311" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C311" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D311" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E311" s="3"/>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A312" s="6" t="s">
         <v>225</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>4</v>
+        <v>116</v>
       </c>
       <c r="C312" s="3" t="s">
         <v>5</v>
@@ -6278,11 +6286,11 @@
       <c r="E312" s="3"/>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A313" s="2" t="s">
-        <v>226</v>
+      <c r="A313" s="6" t="s">
+        <v>225</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>116</v>
+        <v>4</v>
       </c>
       <c r="C313" s="3" t="s">
         <v>5</v>
@@ -6294,58 +6302,58 @@
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A314" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="C314" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E314" s="3"/>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A315" s="2" t="s">
-        <v>88</v>
+        <v>227</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>116</v>
+        <v>8</v>
       </c>
       <c r="C315" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E315" s="3"/>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A316" s="2" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C316" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E316" s="3"/>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A317" s="2" t="s">
-        <v>228</v>
+        <v>39</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>8</v>
+        <v>114</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D317" s="3" t="s">
         <v>6</v>
@@ -6354,22 +6362,22 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A318" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="C318" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E318" s="3"/>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A319" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>114</v>
@@ -6378,19 +6386,19 @@
         <v>9</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E319" s="3"/>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A320" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B320" s="3" t="s">
         <v>114</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D320" s="3" t="s">
         <v>6</v>
@@ -6399,10 +6407,10 @@
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A321" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B321" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C321" s="3" t="s">
         <v>5</v>
@@ -6414,7 +6422,7 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A322" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>116</v>
@@ -6423,13 +6431,13 @@
         <v>5</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E322" s="3"/>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A323" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B323" s="3" t="s">
         <v>116</v>
@@ -6438,13 +6446,13 @@
         <v>5</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E323" s="3"/>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A324" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B324" s="3" t="s">
         <v>116</v>
@@ -6453,31 +6461,31 @@
         <v>5</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E324" s="3"/>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A325" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B325" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C325" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D325" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E325" s="3"/>
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A326" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B325" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C325" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D325" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E325" s="3"/>
-    </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A326" s="4" t="s">
-        <v>237</v>
-      </c>
       <c r="B326" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C326" s="3" t="s">
         <v>5</v>
@@ -6485,51 +6493,51 @@
       <c r="D326" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E326" s="3">
-        <v>1</v>
-      </c>
+      <c r="E326" s="3"/>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A327" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>4</v>
+        <v>117</v>
       </c>
       <c r="C327" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E327" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A328" s="2" t="s">
-        <v>239</v>
+      <c r="A328" s="4" t="s">
+        <v>238</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>118</v>
+        <v>4</v>
       </c>
       <c r="C328" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E328" s="3"/>
+        <v>7</v>
+      </c>
+      <c r="E328" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A329" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B329" s="3" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D329" s="3" t="s">
         <v>6</v>
@@ -6538,13 +6546,13 @@
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A330" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D330" s="3" t="s">
         <v>6</v>
@@ -6553,22 +6561,22 @@
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A331" s="2" t="s">
-        <v>43</v>
+        <v>241</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C331" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E331" s="3"/>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A332" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>8</v>
@@ -6583,7 +6591,7 @@
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A333" s="2" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B333" s="3" t="s">
         <v>8</v>
@@ -6592,28 +6600,28 @@
         <v>9</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E333" s="3"/>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A334" s="2" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E334" s="3"/>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A335" s="2" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="B335" s="3" t="s">
         <v>114</v>
@@ -6622,16 +6630,16 @@
         <v>5</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E335" s="3"/>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A336" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="C336" s="3" t="s">
         <v>5</v>
@@ -6643,10 +6651,10 @@
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A337" s="2" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="C337" s="3" t="s">
         <v>5</v>
@@ -6658,37 +6666,37 @@
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A338" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C338" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E338" s="3"/>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A339" s="2" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>10</v>
+        <v>115</v>
       </c>
       <c r="C339" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E339" s="3"/>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A340" s="2" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="B340" s="3" t="s">
         <v>10</v>
@@ -6697,13 +6705,13 @@
         <v>5</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E340" s="3"/>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A341" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>10</v>
@@ -6712,13 +6720,13 @@
         <v>5</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E341" s="3"/>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A342" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>10</v>
@@ -6733,7 +6741,7 @@
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A343" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>10</v>
@@ -6742,19 +6750,19 @@
         <v>5</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E343" s="3"/>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A344" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D344" s="3" t="s">
         <v>7</v>
@@ -6763,28 +6771,28 @@
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A345" s="2" t="s">
-        <v>242</v>
+        <v>70</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C345" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E345" s="3"/>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A346" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="C346" s="3" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D346" s="3" t="s">
         <v>6</v>
@@ -6793,7 +6801,7 @@
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A347" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B347" s="3" t="s">
         <v>114</v>
@@ -6802,13 +6810,13 @@
         <v>5</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E347" s="3"/>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A348" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>114</v>
@@ -6817,13 +6825,13 @@
         <v>5</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E348" s="3"/>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A349" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B349" s="3" t="s">
         <v>114</v>
@@ -6838,7 +6846,7 @@
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A350" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B350" s="3" t="s">
         <v>114</v>
@@ -6847,13 +6855,13 @@
         <v>5</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E350" s="3"/>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A351" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B351" s="3" t="s">
         <v>114</v>
@@ -6862,13 +6870,13 @@
         <v>5</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E351" s="3"/>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A352" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B352" s="3" t="s">
         <v>114</v>
@@ -6877,43 +6885,58 @@
         <v>5</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E352" s="3"/>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A353" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="C353" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E353" s="3"/>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A354" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B354" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C354" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D354" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E354" s="3"/>
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A355" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="B354" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C354" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D354" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E354" s="3"/>
+      <c r="B355" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C355" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D355" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E355" s="3"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D354">
-    <sortCondition ref="A2:A354"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D355">
+    <sortCondition ref="A2:A355"/>
   </sortState>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
